--- a/backend/Rwanda/carbon-credits.xlsx
+++ b/backend/Rwanda/carbon-credits.xlsx
@@ -608,7 +608,7 @@
     <row r="3" ht="15.5" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>CO2 emited - {model} scenario</t>
+          <t>CO2 emited - CleanStep scenario</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="6" ht="15.5" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>△▲{model} vs. BAU</t>
+          <t>△▲CleanStep vs. BAU</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -764,40 +764,40 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>0</v>
+        <v>21.61017358638736</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>0</v>
+        <v>20.60189269210638</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0</v>
+        <v>19.83817666585722</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0</v>
+        <v>19.07446063960807</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0</v>
+        <v>18.31074461335891</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0</v>
+        <v>17.54702858710975</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>0</v>
+        <v>16.7833125608606</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>0</v>
+        <v>16.43569213193877</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>0</v>
+        <v>16.3666828952225</v>
       </c>
       <c r="L6" s="11" t="n">
-        <v>0</v>
+        <v>16.29767365850622</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>0</v>
+        <v>16.22866442178994</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>0</v>
+        <v>16.15965518507367</v>
       </c>
       <c r="O6" s="8" t="n"/>
     </row>
@@ -902,7 +902,7 @@
     <row r="9" ht="15.5" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>CO2 equivalent avoided in the {model}</t>
+          <t>CO2 equivalent avoided in the CleanStep</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1049,7 +1049,7 @@
     <row r="12" ht="15.5" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Potential income from Carbon Credits in the {model} Plan - right</t>
+          <t>Potential income from Carbon Credits in the CleanStep Plan - right</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">

--- a/backend/Rwanda/carbon-credits.xlsx
+++ b/backend/Rwanda/carbon-credits.xlsx
@@ -865,37 +865,37 @@
         <v>0</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0.6149368591495517</v>
+        <v>0</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1.319440920323566</v>
+        <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>2.023944981497584</v>
+        <v>0</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>2.728449042671592</v>
+        <v>0</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>3.4329531038456</v>
+        <v>0</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>4.137457165019617</v>
+        <v>0</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>4.490574445147783</v>
+        <v>0</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>4.666684116231623</v>
+        <v>0</v>
       </c>
       <c r="L8" s="11" t="n">
-        <v>4.842793787315463</v>
+        <v>0</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>5.018903458399294</v>
+        <v>0</v>
       </c>
       <c r="N8" s="11" t="n">
-        <v>5.195013129483135</v>
+        <v>0</v>
       </c>
       <c r="O8" s="8" t="n"/>
     </row>
@@ -914,37 +914,37 @@
         <v>0</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>0.9573166470064478</v>
+        <v>0</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1.927744790062295</v>
+        <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>2.898172933118151</v>
+        <v>0</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>3.868601076174</v>
+        <v>0</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>4.839029219229856</v>
+        <v>0</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>5.809457362285712</v>
+        <v>0</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>5.864625884171028</v>
+        <v>0</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>5.741268692546351</v>
+        <v>0</v>
       </c>
       <c r="L9" s="11" t="n">
-        <v>5.617911500921664</v>
+        <v>0</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>5.494554309296978</v>
+        <v>0</v>
       </c>
       <c r="N9" s="11" t="n">
-        <v>5.371197117672301</v>
+        <v>0</v>
       </c>
       <c r="O9" s="8" t="n"/>
     </row>
@@ -963,37 +963,37 @@
         <v>0</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>6.149368591495517</v>
+        <v>0</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>13.19440920323567</v>
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>20.23944981497584</v>
+        <v>0</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>27.28449042671592</v>
+        <v>0</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>34.329531038456</v>
+        <v>0</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>41.37457165019617</v>
+        <v>0</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>44.90574445147783</v>
+        <v>0</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>46.66684116231623</v>
+        <v>0</v>
       </c>
       <c r="L10" s="11" t="n">
-        <v>48.42793787315463</v>
+        <v>0</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>50.18903458399294</v>
+        <v>0</v>
       </c>
       <c r="N10" s="11" t="n">
-        <v>51.95013129483135</v>
+        <v>0</v>
       </c>
       <c r="O10" s="8" t="n"/>
     </row>
@@ -1012,37 +1012,37 @@
         <v>0</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>9.573166470064479</v>
+        <v>0</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>19.27744790062295</v>
+        <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>28.98172933118151</v>
+        <v>0</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>38.68601076173999</v>
+        <v>0</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>48.39029219229856</v>
+        <v>0</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>58.09457362285712</v>
+        <v>0</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>58.64625884171028</v>
+        <v>0</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>57.4126869254635</v>
+        <v>0</v>
       </c>
       <c r="L11" s="11" t="n">
-        <v>56.17911500921664</v>
+        <v>0</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>54.94554309296979</v>
+        <v>0</v>
       </c>
       <c r="N11" s="11" t="n">
-        <v>53.71197117672301</v>
+        <v>0</v>
       </c>
       <c r="O11" s="8" t="n"/>
     </row>
